--- a/reports/Technical_Analysis_Report.xlsx
+++ b/reports/Technical_Analysis_Report.xlsx
@@ -452,11 +452,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
@@ -543,6 +543,42 @@
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>ML Prediction Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>75.5% chance up</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>75.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Target Price</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2500.00</t>
         </is>
       </c>
     </row>
@@ -680,7 +716,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1373.170117481173</v>
+        <v>1373.170117451961</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +726,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1563.995007445396</v>
+        <v>1563.995007445397</v>
       </c>
     </row>
     <row r="14">
@@ -720,7 +756,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09021079227236396</v>
+        <v>0.09021079227236456</v>
       </c>
     </row>
     <row r="17">
@@ -730,7 +766,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.1199626544136499</v>
+        <v>-0.1199626544136457</v>
       </c>
     </row>
     <row r="18">
@@ -950,7 +986,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.194890357277348</v>
+        <v>0.1948903572773479</v>
       </c>
     </row>
     <row r="40">
@@ -980,7 +1016,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-290055726.7096</v>
+        <v>-290055726.7096003</v>
       </c>
     </row>
     <row r="43">
@@ -990,7 +1026,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>27.2181449232814</v>
+        <v>27.21814492328141</v>
       </c>
     </row>
     <row r="44">
@@ -1170,7 +1206,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0702080222189161</v>
+        <v>0.07020802221891606</v>
       </c>
     </row>
     <row r="62">
@@ -1180,7 +1216,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7527196512587002</v>
+        <v>-0.7527196512586872</v>
       </c>
     </row>
     <row r="63">
@@ -1303,13 +1339,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>RISK ASSESSMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Risk/Reward Ratio</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Maximum Loss</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100.00</t>
         </is>
       </c>
     </row>

--- a/reports/Technical_Analysis_Report.xlsx
+++ b/reports/Technical_Analysis_Report.xlsx
@@ -452,11 +452,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
@@ -543,42 +543,6 @@
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>ML Prediction Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>75.5% chance up</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>75.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Target Price</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2500.00</t>
         </is>
       </c>
     </row>
@@ -1339,49 +1303,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>RISK ASSESSMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Stop Loss</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2400.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Risk/Reward Ratio</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Maximum Loss</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>100.00</t>
         </is>
       </c>
     </row>
